--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8437570D-DCC9-49B6-975D-1E744E0657F7}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A9E20CC-4B50-46E6-B943-E0DC41A598AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1680,90 +1680,176 @@
       <c r="A21" s="13">
         <v>46267</v>
       </c>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="B21" s="14">
+        <v>600</v>
+      </c>
+      <c r="C21" s="14">
+        <v>100</v>
+      </c>
+      <c r="D21" s="14">
+        <v>80</v>
+      </c>
+      <c r="E21" s="14">
+        <v>30</v>
+      </c>
+      <c r="F21" s="14">
+        <v>350</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>280</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B22" s="14">
+        <v>550</v>
+      </c>
+      <c r="C22" s="14">
+        <v>100</v>
+      </c>
+      <c r="D22" s="14">
+        <v>90</v>
+      </c>
+      <c r="E22" s="14">
+        <v>25</v>
+      </c>
+      <c r="F22" s="14">
+        <v>250</v>
+      </c>
+      <c r="G22" s="14">
+        <v>5</v>
+      </c>
+      <c r="H22" s="14">
+        <v>400</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1415</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
+        <v>25</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B23" s="14">
+        <v>600</v>
+      </c>
+      <c r="C23" s="14">
+        <v>100</v>
+      </c>
+      <c r="D23" s="14">
+        <v>0</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="14">
+        <v>250</v>
+      </c>
+      <c r="G23" s="14">
+        <v>5</v>
+      </c>
+      <c r="H23" s="14">
+        <v>400</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B24" s="14">
+        <v>700</v>
+      </c>
+      <c r="C24" s="14">
+        <v>0</v>
+      </c>
+      <c r="D24" s="14">
+        <v>75</v>
+      </c>
+      <c r="E24" s="14">
+        <v>45</v>
+      </c>
+      <c r="F24" s="14">
+        <v>0</v>
+      </c>
+      <c r="G24" s="14">
+        <v>0</v>
+      </c>
+      <c r="H24" s="14">
+        <v>600</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+        <v>20</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="134" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A9E20CC-4B50-46E6-B943-E0DC41A598AF}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EFD341D-1911-44D8-A238-6E4323E52D83}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1853,69 +1853,135 @@
       <c r="N24" s="17"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B25" s="14">
+        <v>650</v>
+      </c>
+      <c r="C25" s="14">
+        <v>90</v>
+      </c>
+      <c r="D25" s="14">
+        <v>95</v>
+      </c>
+      <c r="E25" s="14">
+        <v>0</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>453</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1288</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
+        <v>152</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N25" s="17"/>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+      <c r="A26" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B26" s="14">
+        <v>630</v>
+      </c>
+      <c r="C26" s="14">
+        <v>100</v>
+      </c>
+      <c r="D26" s="14">
+        <v>60</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0</v>
+      </c>
+      <c r="F26" s="14">
+        <v>200</v>
+      </c>
+      <c r="G26" s="14">
+        <v>4</v>
+      </c>
+      <c r="H26" s="14">
+        <v>400</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N26" s="17"/>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B27" s="14">
+        <v>550</v>
+      </c>
+      <c r="C27" s="14">
+        <v>100</v>
+      </c>
+      <c r="D27" s="14">
+        <v>75</v>
+      </c>
+      <c r="E27" s="14">
+        <v>80</v>
+      </c>
+      <c r="F27" s="14">
+        <v>350</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>280</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
+        <v>5</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8EFD341D-1911-44D8-A238-6E4323E52D83}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE41E0AB-BDE0-4A07-9AAE-9703069D480E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1985,91 +1985,179 @@
       <c r="N27" s="17"/>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B28" s="14">
+        <v>600</v>
+      </c>
+      <c r="C28" s="14">
+        <v>90</v>
+      </c>
+      <c r="D28" s="14">
+        <v>45</v>
+      </c>
+      <c r="E28" s="14">
+        <v>30</v>
+      </c>
+      <c r="F28" s="14">
+        <v>350</v>
+      </c>
+      <c r="G28" s="14">
+        <v>7</v>
+      </c>
+      <c r="H28" s="14">
+        <v>250</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1365</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
+        <v>75</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N28" s="17"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B29" s="14">
+        <v>580</v>
+      </c>
+      <c r="C29" s="14">
+        <v>100</v>
+      </c>
+      <c r="D29" s="14">
+        <v>0</v>
+      </c>
+      <c r="E29" s="14">
+        <v>0</v>
+      </c>
+      <c r="F29" s="14">
+        <v>200</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4</v>
+      </c>
+      <c r="H29" s="14">
+        <v>420</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
+        <v>140</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N29" s="17"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B30" s="14">
+        <v>600</v>
+      </c>
+      <c r="C30" s="14">
+        <v>90</v>
+      </c>
+      <c r="D30" s="14">
+        <v>65</v>
+      </c>
+      <c r="E30" s="14">
+        <v>55</v>
+      </c>
+      <c r="F30" s="14">
+        <v>250</v>
+      </c>
+      <c r="G30" s="14">
+        <v>5</v>
+      </c>
+      <c r="H30" s="14">
+        <v>350</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
+        <v>30</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N30" s="17"/>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B31" s="14">
+        <v>650</v>
+      </c>
+      <c r="C31" s="14">
+        <v>0</v>
+      </c>
+      <c r="D31" s="14">
+        <v>75</v>
+      </c>
+      <c r="E31" s="14">
+        <v>0</v>
+      </c>
+      <c r="F31" s="14">
+        <v>0</v>
+      </c>
+      <c r="G31" s="14">
+        <v>0</v>
+      </c>
+      <c r="H31" s="14">
+        <v>420</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
+        <v>295</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE41E0AB-BDE0-4A07-9AAE-9703069D480E}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5792FA9A-59CF-4038-A719-BA25026D81D8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2161,29 +2161,53 @@
       <c r="N31" s="17"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B32" s="14">
+        <v>420</v>
+      </c>
+      <c r="C32" s="14">
+        <v>0</v>
+      </c>
+      <c r="D32" s="14">
+        <v>50</v>
+      </c>
+      <c r="E32" s="14">
+        <v>0</v>
+      </c>
+      <c r="F32" s="14">
+        <v>0</v>
+      </c>
+      <c r="G32" s="14">
+        <v>0</v>
+      </c>
+      <c r="H32" s="14">
+        <v>740</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
+        <v>230</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N32" s="17"/>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="13"/>
+      <c r="A33" s="13">
+        <v>46279</v>
+      </c>
       <c r="B33" s="14"/>
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5792FA9A-59CF-4038-A719-BA25026D81D8}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFC5A2E9-3236-4A16-A5CF-87E7CD828082}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2208,50 +2208,94 @@
       <c r="A33" s="13">
         <v>46279</v>
       </c>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="B33" s="14">
+        <v>430</v>
+      </c>
+      <c r="C33" s="14">
+        <v>90</v>
+      </c>
+      <c r="D33" s="14">
+        <v>120</v>
+      </c>
+      <c r="E33" s="14">
+        <v>70</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>450</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
+        <v>80</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N33" s="17"/>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B34" s="14">
+        <v>480</v>
+      </c>
+      <c r="C34" s="14">
+        <v>90</v>
+      </c>
+      <c r="D34" s="14">
+        <v>45</v>
+      </c>
+      <c r="E34" s="14">
+        <v>15</v>
+      </c>
+      <c r="F34" s="14">
+        <v>350</v>
+      </c>
+      <c r="G34" s="14">
+        <v>7</v>
+      </c>
+      <c r="H34" s="14">
+        <v>300</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
+        <v>160</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N34" s="17"/>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
+      <c r="A35" s="13">
+        <v>46281</v>
+      </c>
       <c r="B35" s="14"/>
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
@@ -2273,7 +2317,9 @@
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
+      <c r="A36" s="13">
+        <v>46282</v>
+      </c>
       <c r="B36" s="14"/>
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
@@ -2295,7 +2341,9 @@
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13">
+        <v>46283</v>
+      </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
@@ -2317,7 +2365,9 @@
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+      <c r="A38" s="13">
+        <v>46284</v>
+      </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFC5A2E9-3236-4A16-A5CF-87E7CD828082}"/>
+  <xr:revisionPtr revIDLastSave="308" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25334BA6-44AE-4FA6-B7FE-A5BB3558238B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,9 @@
   <si>
     <t>Very Unsatisfied</t>
   </si>
+  <si>
+    <t>satisfied</t>
+  </si>
 </sst>
 </file>
 
@@ -343,7 +346,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -366,11 +369,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB7B7B7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -414,6 +428,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1341,21 +1358,21 @@
         <v>0</v>
       </c>
       <c r="F13" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="G13" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H13" s="14">
         <v>250</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1240</v>
+        <v>1140</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1649,21 +1666,21 @@
         <v>40</v>
       </c>
       <c r="F20" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
         <v>350</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1415</v>
+        <v>1365</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1957,21 +1974,21 @@
         <v>80</v>
       </c>
       <c r="F27" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G27" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H27" s="14">
         <v>280</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1435</v>
+        <v>1385</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>56</v>
@@ -2262,24 +2279,24 @@
         <v>45</v>
       </c>
       <c r="E34" s="14">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F34" s="14">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G34" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H34" s="14">
         <v>300</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>1280</v>
+        <v>1215</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>57</v>
@@ -2296,96 +2313,176 @@
       <c r="A35" s="13">
         <v>46281</v>
       </c>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="B35" s="14">
+        <v>440</v>
+      </c>
+      <c r="C35" s="14">
+        <v>90</v>
+      </c>
+      <c r="D35" s="14">
+        <v>85</v>
+      </c>
+      <c r="E35" s="14">
+        <v>0</v>
+      </c>
+      <c r="F35" s="14">
+        <v>350</v>
+      </c>
+      <c r="G35" s="14">
+        <v>7</v>
+      </c>
+      <c r="H35" s="14">
+        <v>390</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
+        <v>85</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N35" s="17"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13">
         <v>46282</v>
       </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="B36" s="14">
+        <v>500</v>
+      </c>
+      <c r="C36" s="14">
+        <v>90</v>
+      </c>
+      <c r="D36" s="14">
+        <v>100</v>
+      </c>
+      <c r="E36" s="14">
+        <v>55</v>
+      </c>
+      <c r="F36" s="14">
+        <v>200</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>350</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
+        <v>145</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N36" s="17"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13">
         <v>46283</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="B37" s="14">
+        <v>420</v>
+      </c>
+      <c r="C37" s="14">
+        <v>90</v>
+      </c>
+      <c r="D37" s="14">
+        <v>95</v>
+      </c>
+      <c r="E37" s="14">
+        <v>4</v>
+      </c>
+      <c r="F37" s="14">
+        <v>250</v>
+      </c>
+      <c r="G37" s="14">
+        <v>5</v>
+      </c>
+      <c r="H37" s="14">
+        <v>430</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1289</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
+        <v>151</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N37" s="17"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="13">
         <v>46284</v>
       </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="B38" s="14">
+        <v>550</v>
+      </c>
+      <c r="C38" s="14">
+        <v>0</v>
+      </c>
+      <c r="D38" s="14">
+        <v>65</v>
+      </c>
+      <c r="E38" s="14">
+        <v>75</v>
+      </c>
+      <c r="F38" s="14">
+        <v>0</v>
+      </c>
+      <c r="G38" s="14">
+        <v>0</v>
+      </c>
+      <c r="H38" s="14">
+        <v>500</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
+        <v>250</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -10393,12 +10490,12 @@
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+      <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
-      <formula1>"High,Medium,Low"</formula1>
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L35 L37:L401 K36" xr:uid="{00000000-0002-0000-0100-000001000000}">
+      <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="308" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25334BA6-44AE-4FA6-B7FE-A5BB3558238B}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5FB3722-B81C-4B28-846B-5CB452EB0CFC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -425,12 +425,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -918,74 +918,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="21">
         <v>12624002</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="21"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -2389,7 +2389,7 @@
       <c r="K36" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L36" s="21" t="s">
+      <c r="L36" s="18" t="s">
         <v>65</v>
       </c>
       <c r="M36" s="16" t="s">
@@ -2486,47 +2486,91 @@
       <c r="N38" s="17"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B39" s="14">
+        <v>600</v>
+      </c>
+      <c r="C39" s="14">
+        <v>0</v>
+      </c>
+      <c r="D39" s="14">
+        <v>95</v>
+      </c>
+      <c r="E39" s="14">
+        <v>0</v>
+      </c>
+      <c r="F39" s="14">
+        <v>0</v>
+      </c>
+      <c r="G39" s="14">
+        <v>0</v>
+      </c>
+      <c r="H39" s="14">
+        <v>545</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
+        <v>200</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N39" s="17"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B40" s="14">
+        <v>480</v>
+      </c>
+      <c r="C40" s="14">
+        <v>90</v>
+      </c>
+      <c r="D40" s="14">
+        <v>100</v>
+      </c>
+      <c r="E40" s="14">
+        <v>75</v>
+      </c>
+      <c r="F40" s="14">
+        <v>200</v>
+      </c>
+      <c r="G40" s="14">
+        <v>4</v>
+      </c>
+      <c r="H40" s="14">
+        <v>320</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1265</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
+        <v>175</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5FB3722-B81C-4B28-846B-5CB452EB0CFC}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D4A64C2-B352-4A96-9068-F17EB3ACB37E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2411,7 +2411,7 @@
         <v>95</v>
       </c>
       <c r="E37" s="14">
-        <v>4</v>
+        <v>85</v>
       </c>
       <c r="F37" s="14">
         <v>250</v>
@@ -2424,11 +2424,11 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1289</v>
+        <v>1370</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>151</v>
+        <v>70</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>57</v>
@@ -2574,25 +2574,47 @@
       <c r="N40" s="17"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B41" s="14">
+        <v>470</v>
+      </c>
+      <c r="C41" s="14">
+        <v>100</v>
+      </c>
+      <c r="D41" s="14">
+        <v>90</v>
+      </c>
+      <c r="E41" s="14">
+        <v>65</v>
+      </c>
+      <c r="F41" s="14">
+        <v>350</v>
+      </c>
+      <c r="G41" s="14">
+        <v>7</v>
+      </c>
+      <c r="H41" s="14">
+        <v>230</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1305</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
+        <v>135</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="345" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D4A64C2-B352-4A96-9068-F17EB3ACB37E}"/>
+  <xr:revisionPtr revIDLastSave="381" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EE61C02-1726-4F21-8FF6-3D2723E3AACD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -529,10 +529,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2618,69 +2614,135 @@
       <c r="N41" s="17"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B42" s="14">
+        <v>500</v>
+      </c>
+      <c r="C42" s="14">
+        <v>100</v>
+      </c>
+      <c r="D42" s="14">
+        <v>55</v>
+      </c>
+      <c r="E42" s="14">
+        <v>0</v>
+      </c>
+      <c r="F42" s="14">
+        <v>350</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>330</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1335</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
+        <v>105</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N42" s="17"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B43" s="14">
+        <v>465</v>
+      </c>
+      <c r="C43" s="14">
+        <v>100</v>
+      </c>
+      <c r="D43" s="14">
+        <v>85</v>
+      </c>
+      <c r="E43" s="14">
+        <v>70</v>
+      </c>
+      <c r="F43" s="14">
+        <v>150</v>
+      </c>
+      <c r="G43" s="14">
+        <v>3</v>
+      </c>
+      <c r="H43" s="14">
+        <v>390</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B44" s="14">
+        <v>510</v>
+      </c>
+      <c r="C44" s="14">
+        <v>90</v>
+      </c>
+      <c r="D44" s="14">
+        <v>0</v>
+      </c>
+      <c r="E44" s="14">
+        <v>65</v>
+      </c>
+      <c r="F44" s="14">
+        <v>250</v>
+      </c>
+      <c r="G44" s="14">
+        <v>5</v>
+      </c>
+      <c r="H44" s="14">
+        <v>415</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
+        <v>110</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="381" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EE61C02-1726-4F21-8FF6-3D2723E3AACD}"/>
+  <xr:revisionPtr revIDLastSave="550" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C192F8C-ACC3-4993-AD00-1EB161BBD5BC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,9 +232,6 @@
   </si>
   <si>
     <t>Very Unsatisfied</t>
-  </si>
-  <si>
-    <t>satisfied</t>
   </si>
 </sst>
 </file>
@@ -529,6 +526,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -2386,7 +2387,7 @@
         <v>49</v>
       </c>
       <c r="L36" s="18" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
         <v>59</v>
@@ -2746,333 +2747,663 @@
       <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B45" s="14">
+        <v>550</v>
+      </c>
+      <c r="C45" s="14">
+        <v>100</v>
+      </c>
+      <c r="D45" s="14">
+        <v>0</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>50</v>
+      </c>
+      <c r="G45" s="14">
+        <v>1</v>
+      </c>
+      <c r="H45" s="14">
+        <v>670</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B46" s="14">
+        <v>580</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>0</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>790</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
+        <v>70</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N46" s="17"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>0</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>970</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N47" s="17"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B48" s="14">
+        <v>450</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>0</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>900</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N48" s="17"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B49" s="14">
+        <v>610</v>
+      </c>
+      <c r="C49" s="14">
+        <v>100</v>
+      </c>
+      <c r="D49" s="14">
+        <v>0</v>
+      </c>
+      <c r="E49" s="14">
+        <v>0</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>640</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
+        <v>90</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N49" s="17"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B50" s="14">
+        <v>640</v>
+      </c>
+      <c r="C50" s="14">
+        <v>100</v>
+      </c>
+      <c r="D50" s="14">
+        <v>90</v>
+      </c>
+      <c r="E50" s="14">
+        <v>50</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>500</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N50" s="17"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B51" s="14">
+        <v>650</v>
+      </c>
+      <c r="C51" s="14">
+        <v>100</v>
+      </c>
+      <c r="D51" s="14">
+        <v>75</v>
+      </c>
+      <c r="E51" s="14">
+        <v>90</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>480</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1395</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
+        <v>45</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N51" s="17"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B52" s="14">
+        <v>600</v>
+      </c>
+      <c r="C52" s="14">
+        <v>100</v>
+      </c>
+      <c r="D52" s="14">
+        <v>80</v>
+      </c>
+      <c r="E52" s="14">
+        <v>45</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>520</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1345</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
+        <v>95</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N52" s="17"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B53" s="14">
+        <v>620</v>
+      </c>
+      <c r="C53" s="14">
+        <v>100</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>0</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>610</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
+        <v>110</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N53" s="17"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B54" s="14">
+        <v>640</v>
+      </c>
+      <c r="C54" s="14">
+        <v>0</v>
+      </c>
+      <c r="D54" s="14">
+        <v>120</v>
+      </c>
+      <c r="E54" s="14">
+        <v>65</v>
+      </c>
+      <c r="F54" s="14">
+        <v>200</v>
+      </c>
+      <c r="G54" s="14">
+        <v>4</v>
+      </c>
+      <c r="H54" s="14">
+        <v>370</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1395</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
+        <v>45</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N54" s="17"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B55" s="14">
+        <v>700</v>
+      </c>
+      <c r="C55" s="14">
+        <v>100</v>
+      </c>
+      <c r="D55" s="14">
+        <v>0</v>
+      </c>
+      <c r="E55" s="14">
+        <v>0</v>
+      </c>
+      <c r="F55" s="14">
+        <v>0</v>
+      </c>
+      <c r="G55" s="14">
+        <v>0</v>
+      </c>
+      <c r="H55" s="14">
+        <v>520</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N55" s="17"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B56" s="14">
+        <v>690</v>
+      </c>
+      <c r="C56" s="14">
+        <v>100</v>
+      </c>
+      <c r="D56" s="14">
+        <v>0</v>
+      </c>
+      <c r="E56" s="14">
+        <v>50</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>480</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N56" s="17"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B57" s="14">
+        <v>620</v>
+      </c>
+      <c r="C57" s="14">
+        <v>100</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>540</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
+        <v>180</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N57" s="17"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B58" s="14">
+        <v>550</v>
+      </c>
+      <c r="C58" s="14">
+        <v>100</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>600</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
+        <v>190</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N58" s="17"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B59" s="14">
+        <v>490</v>
+      </c>
+      <c r="C59" s="14">
+        <v>0</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>820</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">

--- a/12624002.xlsx
+++ b/12624002.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c135914e813e79f/Desktop/python/776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="550" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C192F8C-ACC3-4993-AD00-1EB161BBD5BC}"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="8_{2F929DCF-A852-4FE5-927A-37AC65437CF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C9EC591E-F618-4286-879B-5C92A08646C8}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="F59" s="14">
         <v>0</v>
@@ -3389,11 +3389,11 @@
       </c>
       <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v>1310</v>
+        <v>1395</v>
       </c>
       <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>45</v>
       </c>
       <c r="K59" s="16" t="s">
         <v>57</v>
@@ -3407,201 +3407,399 @@
       <c r="N59" s="17"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B60" s="14">
+        <v>480</v>
+      </c>
+      <c r="C60" s="14">
+        <v>100</v>
+      </c>
+      <c r="D60" s="14">
+        <v>240</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>520</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1340</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
+        <v>100</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N60" s="17"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B61" s="14">
+        <v>550</v>
+      </c>
+      <c r="C61" s="14">
+        <v>100</v>
+      </c>
+      <c r="D61" s="14">
+        <v>330</v>
+      </c>
+      <c r="E61" s="14">
+        <v>45</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>380</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1405</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
+        <v>35</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N61" s="17"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B62" s="14">
+        <v>580</v>
+      </c>
+      <c r="C62" s="14">
+        <v>100</v>
+      </c>
+      <c r="D62" s="14">
+        <v>260</v>
+      </c>
+      <c r="E62" s="14">
+        <v>0</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>440</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
+        <v>60</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N62" s="17"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B63" s="14">
+        <v>530</v>
+      </c>
+      <c r="C63" s="14">
+        <v>100</v>
+      </c>
+      <c r="D63" s="14">
+        <v>280</v>
+      </c>
+      <c r="E63" s="14">
+        <v>0</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>510</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1420</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
+        <v>20</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N63" s="17"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B64" s="14">
+        <v>520</v>
+      </c>
+      <c r="C64" s="14">
+        <v>100</v>
+      </c>
+      <c r="D64" s="14">
+        <v>340</v>
+      </c>
+      <c r="E64" s="14">
+        <v>70</v>
+      </c>
+      <c r="F64" s="14">
+        <v>0</v>
+      </c>
+      <c r="G64" s="14">
+        <v>0</v>
+      </c>
+      <c r="H64" s="14">
+        <v>370</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>1400</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
+        <v>40</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N64" s="17"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B65" s="14">
+        <v>480</v>
+      </c>
+      <c r="C65" s="14">
+        <v>0</v>
+      </c>
+      <c r="D65" s="14">
+        <v>390</v>
+      </c>
+      <c r="E65" s="14">
+        <v>0</v>
+      </c>
+      <c r="F65" s="14">
+        <v>0</v>
+      </c>
+      <c r="G65" s="14">
+        <v>0</v>
+      </c>
+      <c r="H65" s="14">
+        <v>450</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
+        <v>120</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N65" s="17"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B66" s="14">
+        <v>620</v>
+      </c>
+      <c r="C66" s="14">
+        <v>100</v>
+      </c>
+      <c r="D66" s="14">
+        <v>200</v>
+      </c>
+      <c r="E66" s="14">
+        <v>55</v>
+      </c>
+      <c r="F66" s="14">
+        <v>0</v>
+      </c>
+      <c r="G66" s="14">
+        <v>0</v>
+      </c>
+      <c r="H66" s="14">
+        <v>320</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1295</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+        <v>145</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="N66" s="17"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B67" s="14">
+        <v>420</v>
+      </c>
+      <c r="C67" s="14">
+        <v>100</v>
+      </c>
+      <c r="D67" s="14">
+        <v>400</v>
+      </c>
+      <c r="E67" s="14">
+        <v>0</v>
+      </c>
+      <c r="F67" s="14">
+        <v>0</v>
+      </c>
+      <c r="G67" s="14">
+        <v>0</v>
+      </c>
+      <c r="H67" s="14">
+        <v>390</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1310</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
+        <v>130</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N67" s="17"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B68" s="14">
+        <v>630</v>
+      </c>
+      <c r="C68" s="14">
+        <v>0</v>
+      </c>
+      <c r="D68" s="14">
+        <v>0</v>
+      </c>
+      <c r="E68" s="14">
+        <v>90</v>
+      </c>
+      <c r="F68" s="14">
+        <v>200</v>
+      </c>
+      <c r="G68" s="14">
+        <v>4</v>
+      </c>
+      <c r="H68" s="14">
+        <v>470</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
+        <v>50</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>59</v>
+      </c>
       <c r="N68" s="17"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
